--- a/PS_adapted_options.xlsx
+++ b/PS_adapted_options.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/liming/Desktop/LLM&amp;SJT/teacher/final_submittion/content_validity/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C1ABEDF-D683-CA49-B586-6719E9FD00BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CDD22A3-0A90-D445-A104-7B156B8265C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="980" yWindow="500" windowWidth="27820" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -433,10 +433,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>You've observed that during group discussion sessions in class, certain students consistently dominate the conversation, while others hardly say a word. This has been happening for quite a while. What would you do in this situation?</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>After a class quiz, you discover that several students scored far below the class average. These students had performed reasonably well in previous lessons, but this time there's been a noticeable decline. What would you do in this situation?</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -609,18 +605,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>Talk to the students who rarely speak after class and encourage them to participate actively in discussions.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Praise the active students to motivate other students.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Recognize that everyone has their own personality and don't force everyone to participate actively.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>Adjust the group discussion format to ensure every student has an opportunity to speak.</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -778,6 +762,22 @@
   </si>
   <si>
     <t>Communicate with parents to jointly encourage students to maintain their learning motivation.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>You notice that whenever there are group discussions in class, there are always a few students who are active, while others hardly speak at all. This situation has persisted for some time. What would you do in this situation?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Talk to the less vocal students after class to encourage them to participate more actively in discussions.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Praise the active students to motivate others to participate.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Recognize that everyone has their own personality and not force everyone to actively participate.</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -1405,13 +1405,13 @@
         <v>123</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>113</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>2</v>
@@ -1467,7 +1467,7 @@
         <v>7</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F2" s="3">
         <v>2</v>
@@ -1525,7 +1525,7 @@
         <v>8</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F3" s="3">
         <v>1</v>
@@ -1583,7 +1583,7 @@
         <v>9</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F4" s="3">
         <v>0</v>
@@ -1641,7 +1641,7 @@
         <v>10</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F5" s="3">
         <v>1</v>
@@ -1699,7 +1699,7 @@
         <v>13</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
@@ -1757,7 +1757,7 @@
         <v>14</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F7" s="1">
         <v>1</v>
@@ -1815,7 +1815,7 @@
         <v>15</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F8" s="1">
         <v>0</v>
@@ -1873,7 +1873,7 @@
         <v>16</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F9" s="1">
         <v>2</v>
@@ -1925,13 +1925,13 @@
         <v>18</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>19</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F10" s="3">
         <v>0</v>
@@ -1983,13 +1983,13 @@
         <v>18</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F11" s="3">
         <v>2</v>
@@ -2041,13 +2041,13 @@
         <v>18</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>21</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F12" s="3">
         <v>1</v>
@@ -2099,13 +2099,13 @@
         <v>18</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F13" s="3">
         <v>1</v>
@@ -2157,13 +2157,13 @@
         <v>24</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
@@ -2215,13 +2215,13 @@
         <v>24</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F15" s="1">
         <v>1</v>
@@ -2273,13 +2273,13 @@
         <v>24</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F16" s="1">
         <v>1</v>
@@ -2331,13 +2331,13 @@
         <v>24</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F17" s="1">
         <v>2</v>
@@ -2395,7 +2395,7 @@
         <v>31</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F18" s="3">
         <v>1</v>
@@ -2453,7 +2453,7 @@
         <v>32</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F19" s="3">
         <v>0</v>
@@ -2511,7 +2511,7 @@
         <v>33</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F20" s="3">
         <v>2</v>
@@ -2569,7 +2569,7 @@
         <v>34</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F21" s="3">
         <v>1</v>
@@ -2621,13 +2621,13 @@
         <v>36</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>37</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F22" s="1">
         <v>1</v>
@@ -2679,13 +2679,13 @@
         <v>36</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>38</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F23" s="1">
         <v>0</v>
@@ -2737,13 +2737,13 @@
         <v>36</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>39</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F24" s="1">
         <v>1</v>
@@ -2795,13 +2795,13 @@
         <v>36</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>40</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F25" s="1">
         <v>2</v>
@@ -2859,7 +2859,7 @@
         <v>43</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F26" s="3">
         <v>1</v>
@@ -2917,7 +2917,7 @@
         <v>44</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F27" s="3">
         <v>0</v>
@@ -2975,7 +2975,7 @@
         <v>45</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F28" s="3">
         <v>1</v>
@@ -3033,7 +3033,7 @@
         <v>46</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F29" s="3">
         <v>2</v>
@@ -3091,7 +3091,7 @@
         <v>49</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F30" s="1">
         <v>2</v>
@@ -3149,7 +3149,7 @@
         <v>50</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F31" s="1">
         <v>1</v>
@@ -3207,7 +3207,7 @@
         <v>51</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F32" s="1">
         <v>1</v>
@@ -3265,7 +3265,7 @@
         <v>52</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F33" s="1">
         <v>0</v>
@@ -3317,13 +3317,13 @@
         <v>54</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>129</v>
+        <v>212</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>55</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>173</v>
+        <v>213</v>
       </c>
       <c r="F34" s="3">
         <v>1</v>
@@ -3375,13 +3375,13 @@
         <v>54</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>129</v>
+        <v>212</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>174</v>
+        <v>214</v>
       </c>
       <c r="F35" s="3">
         <v>1</v>
@@ -3433,13 +3433,13 @@
         <v>54</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>129</v>
+        <v>212</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>175</v>
+        <v>215</v>
       </c>
       <c r="F36" s="3">
         <v>0</v>
@@ -3491,13 +3491,13 @@
         <v>54</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>129</v>
+        <v>212</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="F37" s="3">
         <v>2</v>
@@ -3549,13 +3549,13 @@
         <v>60</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>61</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F38" s="1">
         <v>2</v>
@@ -3607,13 +3607,13 @@
         <v>60</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>62</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="F39" s="1">
         <v>1</v>
@@ -3665,13 +3665,13 @@
         <v>60</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>63</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="F40" s="1">
         <v>0</v>
@@ -3723,13 +3723,13 @@
         <v>60</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>64</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="F41" s="1">
         <v>1</v>
@@ -3781,13 +3781,13 @@
         <v>66</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>67</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="F42" s="3">
         <v>1</v>
@@ -3839,13 +3839,13 @@
         <v>66</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>68</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="F43" s="3">
         <v>2</v>
@@ -3897,13 +3897,13 @@
         <v>66</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>69</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="F44" s="3">
         <v>1</v>
@@ -3955,13 +3955,13 @@
         <v>66</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>70</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F45" s="3">
         <v>0</v>
@@ -4013,13 +4013,13 @@
         <v>72</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>73</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="F46" s="1">
         <v>2</v>
@@ -4071,13 +4071,13 @@
         <v>72</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>74</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F47" s="1">
         <v>1</v>
@@ -4129,13 +4129,13 @@
         <v>72</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>75</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="F48" s="1">
         <v>0</v>
@@ -4187,13 +4187,13 @@
         <v>72</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>76</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F49" s="1">
         <v>1</v>
@@ -4245,13 +4245,13 @@
         <v>78</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>79</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="F50" s="3">
         <v>1</v>
@@ -4303,13 +4303,13 @@
         <v>78</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>80</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F51" s="3">
         <v>0</v>
@@ -4361,13 +4361,13 @@
         <v>78</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>81</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="F52" s="3">
         <v>2</v>
@@ -4419,13 +4419,13 @@
         <v>78</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>82</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F53" s="3">
         <v>1</v>
@@ -4477,13 +4477,13 @@
         <v>84</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>85</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="F54" s="1">
         <v>2</v>
@@ -4535,13 +4535,13 @@
         <v>84</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>86</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="F55" s="1">
         <v>1</v>
@@ -4593,13 +4593,13 @@
         <v>84</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>87</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="F56" s="1">
         <v>0</v>
@@ -4651,13 +4651,13 @@
         <v>84</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>88</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="F57" s="1">
         <v>1</v>
@@ -4709,13 +4709,13 @@
         <v>90</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>91</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F58" s="3">
         <v>1</v>
@@ -4767,13 +4767,13 @@
         <v>90</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>92</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="F59" s="3">
         <v>1</v>
@@ -4825,13 +4825,13 @@
         <v>90</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>93</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F60" s="3">
         <v>2</v>
@@ -4883,13 +4883,13 @@
         <v>90</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>94</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F61" s="3">
         <v>0</v>
@@ -4941,13 +4941,13 @@
         <v>96</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>97</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="F62" s="1">
         <v>2</v>
@@ -4999,13 +4999,13 @@
         <v>96</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>98</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F63" s="1">
         <v>1</v>
@@ -5057,13 +5057,13 @@
         <v>96</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>99</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F64" s="1">
         <v>1</v>
@@ -5115,13 +5115,13 @@
         <v>96</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>100</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F65" s="1">
         <v>0</v>
@@ -5173,13 +5173,13 @@
         <v>102</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>103</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="F66" s="3">
         <v>1</v>
@@ -5231,13 +5231,13 @@
         <v>102</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>104</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="F67" s="3">
         <v>2</v>
@@ -5289,13 +5289,13 @@
         <v>102</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>105</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="F68" s="3">
         <v>1</v>
@@ -5347,13 +5347,13 @@
         <v>102</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>106</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="F69" s="3">
         <v>0</v>
@@ -5405,13 +5405,13 @@
         <v>108</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>109</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="F70" s="1">
         <v>1</v>
@@ -5463,13 +5463,13 @@
         <v>108</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>110</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="F71" s="1">
         <v>0</v>
@@ -5521,13 +5521,13 @@
         <v>108</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>111</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="F72" s="1">
         <v>1</v>
@@ -5579,13 +5579,13 @@
         <v>108</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>112</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="F73" s="1">
         <v>2</v>
